--- a/InfoMath/ExemplesClasse/Graphes-_Exemples_notes_de_cours.xlsx
+++ b/InfoMath/ExemplesClasse/Graphes-_Exemples_notes_de_cours.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cegepGit\InfoMath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cegepGit\InfoMath\ExemplesClasse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ECCD967-2AB0-44BB-8F95-DDE5B8259C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2FE940-4F3A-42CE-B0B0-A9C0ABB6868F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données" sheetId="1" r:id="rId1"/>
@@ -51,8 +51,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
   <si>
     <t>Individu</t>
   </si>
@@ -196,6 +218,27 @@
   </si>
   <si>
     <t>Remarque : 50% des étudiants ont pris 7min30 et moins pour ecrire un texte de 150 mots</t>
+  </si>
+  <si>
+    <t>Mode :</t>
+  </si>
+  <si>
+    <t>Main droite</t>
+  </si>
+  <si>
+    <t>[60,70[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendance: Mode </t>
+  </si>
+  <si>
+    <t>Tendance : Moyenne car distribution normale</t>
+  </si>
+  <si>
+    <t>Tendance: Moyenne car distribuion normale</t>
+  </si>
+  <si>
+    <t>Tendance : Mode car bimodale</t>
   </si>
 </sst>
 </file>
@@ -581,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -779,13 +822,22 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,7 +926,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -900,6 +952,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4E1F-4A03-913C-D33DD2736ECB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -915,6 +972,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4E1F-4A03-913C-D33DD2736ECB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1173,7 +1235,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1308,7 +1370,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1433,7 +1495,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1594,7 +1656,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1754,7 +1816,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1879,7 +1941,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2040,7 +2102,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2193,7 +2255,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2318,7 +2380,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2479,7 +2541,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="fr-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2665,7 +2727,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2791,7 +2853,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="fr-FR"/>
+              <a:endParaRPr lang="fr-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7784,7 +7846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4109E05-FC33-4AE5-8B87-91947D6E76AC}">
-  <dimension ref="A2:O32"/>
+  <dimension ref="A2:O35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
@@ -7842,94 +7904,107 @@
       <c r="B7" s="63" t="s">
         <v>33</v>
       </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
       <c r="D7" t="s">
         <v>34</v>
       </c>
+      <c r="E7" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="73"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="69"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="69"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="69"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="J19" s="70" t="s">
+      <c r="J19" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="70"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="J20" s="70" t="s">
+      <c r="J20" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="70"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="68"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="A9:F13"/>
     <mergeCell ref="J19:O19"/>
@@ -8080,7 +8155,10 @@
       <c r="B11" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="60"/>
+      <c r="C11" s="60" cm="1">
+        <f t="array" ref="C11">_xlfn.MODE.MULT(Motiv)</f>
+        <v>4</v>
+      </c>
       <c r="D11" s="64" t="s">
         <v>37</v>
       </c>
@@ -8091,72 +8169,77 @@
       <c r="F11" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="62"/>
+      <c r="G11" s="62">
+        <f>AVERAGE(Motiv)</f>
+        <v>2.9249999999999998</v>
+      </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C12" s="60"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
+      <c r="D12" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
     </row>
     <row r="13" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="L13" s="70" t="s">
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="L13" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="L14" s="70" t="s">
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="L14" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
     </row>
     <row r="16" spans="2:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C18" s="66"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
@@ -8175,13 +8258,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L14:Q14"/>
     <mergeCell ref="D12:E15"/>
     <mergeCell ref="F12:G15"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="L14:Q14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -8312,94 +8395,108 @@
       <c r="B10" t="s">
         <v>33</v>
       </c>
+      <c r="C10">
+        <v>62</v>
+      </c>
       <c r="D10" t="s">
         <v>35</v>
       </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
       <c r="F10" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="60"/>
+      <c r="G10" s="60">
+        <f>MEDIAN(Moy.générale)</f>
+        <v>71</v>
+      </c>
       <c r="H10" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="60"/>
+      <c r="I10" s="60">
+        <f>AVERAGE(Moy.générale)</f>
+        <v>73.125</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
+      <c r="F11" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
     </row>
     <row r="17" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C18" s="67"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
     </row>
     <row r="19" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="67"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="67"/>
-      <c r="K20" s="70" t="s">
+      <c r="K20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="70"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="68"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="K21" s="70" t="s">
+      <c r="K21" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="70"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
@@ -8416,14 +8513,14 @@
         <v>43</v>
       </c>
       <c r="C24" s="66"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
     </row>
     <row r="25" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
     </row>
     <row r="26" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
@@ -8652,74 +8749,84 @@
       <c r="F12" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="60"/>
+      <c r="G12" s="60">
+        <f>MEDIAN(Temps)</f>
+        <v>7.25</v>
+      </c>
       <c r="H12" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="60"/>
+      <c r="I12" s="72">
+        <f>AVERAGE(Temps)</f>
+        <v>7.4022500000000004</v>
+      </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
     </row>
     <row r="16" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
+      <c r="B16" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="73"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
     </row>
     <row r="17" spans="2:17" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="L17" s="70" t="s">
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="L17" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
     </row>
     <row r="18" spans="2:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="66"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="L18" s="70" t="s">
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="L18" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="M18" s="70"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
     </row>
     <row r="19" spans="2:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
     </row>
     <row r="20" spans="2:17" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
@@ -8732,27 +8839,26 @@
         <v>43</v>
       </c>
       <c r="D37" s="66"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
     </row>
     <row r="39" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="L17:Q17"/>
     <mergeCell ref="L18:Q18"/>
     <mergeCell ref="E37:G39"/>
-    <mergeCell ref="F13:G16"/>
-    <mergeCell ref="H13:I16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D19:F19"/>
